--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260709_211320.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
